--- a/StructureDefinition-access-align-in.xlsx
+++ b/StructureDefinition-access-align-in.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2119" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2386" uniqueCount="242">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T23:16:42-05:00</t>
+    <t>2026-03-06T16:03:26-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -363,7 +363,7 @@
     <t>Parameters.parameter</t>
   </si>
   <si>
-    <t>5</t>
+    <t>6</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
@@ -647,7 +647,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSTrackVS|0.7.0</t>
+    <t>https://globalalliantinc.com/access/ValueSet/ACCESSTrackVS|0.9.0</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -656,31 +656,31 @@
     <t>Parameters.parameter:track.part</t>
   </si>
   <si>
-    <t>Parameters.parameter:conditions</t>
-  </si>
-  <si>
-    <t>conditions</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condition {https://globalalliantinc.com/access/StructureDefinition/access-condition|0.7.0}
+    <t>Parameters.parameter:condition</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition {https://globalalliantinc.com/access/StructureDefinition/access-condition|0.9.0}
 </t>
   </si>
   <si>
@@ -693,7 +693,43 @@
     <t>Observation[classCode=OBS, moodCode=EVN, code=ASSERTION, value&lt;Diagnosis]</t>
   </si>
   <si>
-    <t>Parameters.parameter:conditions.part</t>
+    <t>Parameters.parameter:condition.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:referralType</t>
+  </si>
+  <si>
+    <t>referralType</t>
+  </si>
+  <si>
+    <t>Referral Type</t>
+  </si>
+  <si>
+    <t>Indicates how the patient was referred to the ACCESS Model participant. This information helps track recruitment pathways and evaluate outreach effectiveness.</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:referralType.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:referralType.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:referralType.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:referralType.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:referralType.value[x]</t>
+  </si>
+  <si>
+    <t>https://globalalliantinc.com/access/ValueSet/ACCESSReferralTypeVS|0.9.0</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:referralType.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:referralType.part</t>
   </si>
   <si>
     <t>Parameters.parameter:switchConsentAttestation</t>
@@ -1047,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL62"/>
+  <dimension ref="A1:AL70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.3828125" customWidth="true" bestFit="true"/>
@@ -1075,7 +1111,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.0625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.48046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
@@ -3255,7 +3291,7 @@
         <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>75</v>
@@ -4111,7 +4147,7 @@
         <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>75</v>
@@ -4861,7 +4897,7 @@
         <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>75</v>
@@ -5821,7 +5857,7 @@
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
@@ -6571,7 +6607,7 @@
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>75</v>
@@ -6892,7 +6928,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>84</v>
@@ -7439,7 +7475,7 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>145</v>
@@ -7472,13 +7508,11 @@
         <v>75</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>75</v>
+        <v>227</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -7533,7 +7567,7 @@
         <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>75</v>
@@ -7733,8 +7767,864 @@
         <v>75</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="D63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL62">
+  <autoFilter ref="A1:AL70">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7744,7 +8634,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-access-align-in.xlsx
+++ b/StructureDefinition-access-align-in.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2386" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2387" uniqueCount="241">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/StructureDefinition/access-align-in</t>
+    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-align-in</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T16:03:26-05:00</t>
+    <t>2026-03-12T23:55:37-07:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -647,7 +647,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSTrackVS|0.9.0</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.1</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -680,7 +680,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://globalalliantinc.com/access/StructureDefinition/access-condition|0.9.0}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.1}
 </t>
   </si>
   <si>
@@ -696,71 +696,68 @@
     <t>Parameters.parameter:condition.part</t>
   </si>
   <si>
-    <t>Parameters.parameter:referralType</t>
-  </si>
-  <si>
-    <t>referralType</t>
-  </si>
-  <si>
-    <t>Referral Type</t>
-  </si>
-  <si>
-    <t>Indicates how the patient was referred to the ACCESS Model participant. This information helps track recruitment pathways and evaluate outreach effectiveness.</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:referralType.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:referralType.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:referralType.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:referralType.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:referralType.value[x]</t>
-  </si>
-  <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSReferralTypeVS|0.9.0</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:referralType.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:referralType.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:switchConsentAttestation</t>
-  </si>
-  <si>
-    <t>switchConsentAttestation</t>
-  </si>
-  <si>
-    <t>Provider Switch Consent Attestation</t>
-  </si>
-  <si>
-    <t>Boolean flag indicating whether the patient has provided consent to switch from their current ACCESS participant to a new provider. This parameter is required when a patient wishes to align to a different provider after the initial 3-month lock-in period. [legal text goes here]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:switchConsentAttestation.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:switchConsentAttestation.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:switchConsentAttestation.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:switchConsentAttestation.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:switchConsentAttestation.value[x]</t>
+    <t>Parameters.parameter:isProviderReferral</t>
+  </si>
+  <si>
+    <t>isProviderReferral</t>
+  </si>
+  <si>
+    <t>Provider referred?</t>
+  </si>
+  <si>
+    <t>Indicates whether the patient was referred to the ACCESS Model participant by a provider. This information helps track recruitment pathways and evaluate outreach effectiveness.</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:isProviderReferral.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:isProviderReferral.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:isProviderReferral.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:isProviderReferral.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:isProviderReferral.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
+  </si>
+  <si>
+    <t>Parameters.parameter:isProviderReferral.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:isProviderReferral.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:switchConsentAttestation</t>
+  </si>
+  <si>
+    <t>switchConsentAttestation</t>
+  </si>
+  <si>
+    <t>Provider Switch Consent Attestation</t>
+  </si>
+  <si>
+    <t>Boolean flag indicating whether the patient has provided consent to switch from their current ACCESS participant to a new provider. This parameter is required when a patient wishes to align to a different provider after the initial 3-month lock-in period. [legal text goes here]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:switchConsentAttestation.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:switchConsentAttestation.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:switchConsentAttestation.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:switchConsentAttestation.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:switchConsentAttestation.value[x]</t>
   </si>
   <si>
     <t>Parameters.parameter:switchConsentAttestation.resource</t>
@@ -1111,7 +1108,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.48046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.64453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
@@ -7475,7 +7472,7 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>145</v>
@@ -7508,11 +7505,13 @@
         <v>75</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>227</v>
+        <v>75</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -8329,7 +8328,7 @@
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>145</v>
@@ -8409,7 +8408,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>148</v>
@@ -8517,7 +8516,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>153</v>

--- a/StructureDefinition-access-align-in.xlsx
+++ b/StructureDefinition-access-align-in.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2387" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2386" uniqueCount="240">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T23:55:37-07:00</t>
+    <t>2026-04-24T13:45:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This is the profile for the `$align` operation input parameters. When a patient wishes to switch from one ACCESS participant to another after the 3-month lock-in period, the `switchConsentAttestation` parameter must be set to `true` to indicate that the patient has provided consent to switch providers.</t>
+    <t>This is the profile for the `$align` operation input parameters. When a patient wishes to switch from one ACCESS participant to another after the 90-day lock-in period, the `switchConsentAttestation` parameter must be set to `true` to indicate that the patient has provided consent to switch providers.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -351,9 +351,6 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
@@ -539,7 +536,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-access-participant-id-pattern:ACCESS Participant ID must follow the pattern ACCESS#### where #### represents exactly 4 digits (e.g., ACCESS0001, ACCESS1234) {value.matches('^ACCESS\\d{4}$')}</t>
+access-participant-id-pattern:ACCESS Participant ID must follow the pattern ACCES##### where ##### represents exactly 5 digits (e.g., ACCES00001, ACCES12345) {value.matches('^ACCES\\d{5}$')}</t>
   </si>
   <si>
     <t>Parameters.parameter:participantID.resource</t>
@@ -647,7 +644,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.1</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.6</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -680,7 +677,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.1}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.6}
 </t>
   </si>
   <si>
@@ -742,7 +739,7 @@
     <t>Provider Switch Consent Attestation</t>
   </si>
   <si>
-    <t>Boolean flag indicating whether the patient has provided consent to switch from their current ACCESS participant to a new provider. This parameter is required when a patient wishes to align to a different provider after the initial 3-month lock-in period. [legal text goes here]</t>
+    <t>Boolean flag indicating whether the patient has provided consent to switch from their current ACCESS participant to a new provider. This parameter is required when a patient wishes to align to a different provider after the initial 90-day lock-in period. [legal text goes here]</t>
   </si>
   <si>
     <t>Parameters.parameter:switchConsentAttestation.id</t>
@@ -1733,29 +1730,27 @@
       <c r="X6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Y6" s="2"/>
+      <c r="Z6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -1778,10 +1773,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1789,7 +1784,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>77</v>
@@ -1804,13 +1799,13 @@
         <v>85</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1849,17 +1844,17 @@
         <v>75</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AC7" s="2"/>
       <c r="AD7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -1871,7 +1866,7 @@
         <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
@@ -1882,10 +1877,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1908,13 +1903,13 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1965,7 +1960,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -1988,14 +1983,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2014,16 +2009,16 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2073,7 +2068,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2085,7 +2080,7 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
@@ -2096,14 +2091,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2122,19 +2117,19 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>75</v>
@@ -2183,7 +2178,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2195,21 +2190,21 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2232,13 +2227,13 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2289,7 +2284,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>84</v>
@@ -2312,10 +2307,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2338,13 +2333,13 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2395,7 +2390,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2404,7 +2399,7 @@
         <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
@@ -2418,10 +2413,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2444,16 +2439,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2503,7 +2498,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2512,7 +2507,7 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>75</v>
@@ -2526,10 +2521,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2555,13 +2550,13 @@
         <v>75</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2611,7 +2606,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2634,13 +2629,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>75</v>
@@ -2662,13 +2657,13 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2719,7 +2714,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2731,7 +2726,7 @@
         <v>75</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
@@ -2742,10 +2737,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2768,13 +2763,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2825,7 +2820,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2848,14 +2843,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2874,16 +2869,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2933,7 +2928,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -2945,7 +2940,7 @@
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
@@ -2956,10 +2951,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2982,13 +2977,13 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3039,7 +3034,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3051,7 +3046,7 @@
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
@@ -3062,10 +3057,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3088,13 +3083,13 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3103,7 +3098,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>75</v>
@@ -3145,7 +3140,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -3168,10 +3163,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3194,13 +3189,13 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3251,7 +3246,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3260,10 +3255,10 @@
         <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>75</v>
@@ -3274,10 +3269,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3300,16 +3295,16 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3359,7 +3354,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3368,7 +3363,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>75</v>
@@ -3382,10 +3377,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3411,13 +3406,13 @@
         <v>78</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3467,7 +3462,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3490,13 +3485,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>75</v>
@@ -3518,13 +3513,13 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3575,7 +3570,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3587,7 +3582,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3598,10 +3593,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3624,13 +3619,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3681,7 +3676,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3704,14 +3699,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3730,16 +3725,16 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3789,7 +3784,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -3801,7 +3796,7 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
@@ -3812,10 +3807,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3838,13 +3833,13 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3895,7 +3890,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -3907,7 +3902,7 @@
         <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>75</v>
@@ -3918,10 +3913,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3944,13 +3939,13 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3959,7 +3954,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>75</v>
@@ -4001,7 +3996,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>84</v>
@@ -4024,10 +4019,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4050,13 +4045,13 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4107,7 +4102,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4116,7 +4111,7 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>96</v>
@@ -4130,10 +4125,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4156,16 +4151,16 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4215,7 +4210,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4224,7 +4219,7 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>75</v>
@@ -4238,10 +4233,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4267,13 +4262,13 @@
         <v>78</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4323,7 +4318,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4346,13 +4341,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C31" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>75</v>
@@ -4374,13 +4369,13 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4431,7 +4426,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4443,7 +4438,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
@@ -4454,10 +4449,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4480,13 +4475,13 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4537,7 +4532,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4560,14 +4555,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4586,16 +4581,16 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4645,7 +4640,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4657,7 +4652,7 @@
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
@@ -4668,10 +4663,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4694,13 +4689,13 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4751,7 +4746,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -4763,7 +4758,7 @@
         <v>75</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>75</v>
@@ -4774,10 +4769,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4800,13 +4795,13 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4815,7 +4810,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>75</v>
@@ -4857,7 +4852,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>84</v>
@@ -4880,10 +4875,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4906,13 +4901,13 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4963,7 +4958,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -4972,7 +4967,7 @@
         <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>96</v>
@@ -4986,14 +4981,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5012,16 +5007,16 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="N37" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5071,7 +5066,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5089,15 +5084,15 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5123,13 +5118,13 @@
         <v>78</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5179,7 +5174,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5202,13 +5197,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>75</v>
@@ -5230,13 +5225,13 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5287,7 +5282,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5299,7 +5294,7 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5310,10 +5305,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5336,13 +5331,13 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5393,7 +5388,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5416,14 +5411,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5442,16 +5437,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5501,7 +5496,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5513,7 +5508,7 @@
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>75</v>
@@ -5524,10 +5519,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5550,13 +5545,13 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5607,7 +5602,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5619,7 +5614,7 @@
         <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>75</v>
@@ -5630,10 +5625,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5656,13 +5651,13 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5671,7 +5666,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>75</v>
@@ -5713,7 +5708,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>84</v>
@@ -5736,10 +5731,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5762,13 +5757,13 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5795,11 +5790,11 @@
         <v>75</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -5817,7 +5812,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -5826,7 +5821,7 @@
         <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>96</v>
@@ -5840,10 +5835,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5866,16 +5861,16 @@
         <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5925,7 +5920,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -5934,7 +5929,7 @@
         <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>75</v>
@@ -5948,10 +5943,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5977,13 +5972,13 @@
         <v>78</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6033,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6056,13 +6051,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>75</v>
@@ -6084,13 +6079,13 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6141,7 +6136,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6153,7 +6148,7 @@
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
@@ -6164,10 +6159,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6190,13 +6185,13 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6247,7 +6242,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6270,14 +6265,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6296,16 +6291,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6355,7 +6350,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6367,7 +6362,7 @@
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
@@ -6378,10 +6373,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6404,13 +6399,13 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6461,7 +6456,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6473,7 +6468,7 @@
         <v>75</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>75</v>
@@ -6484,10 +6479,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6510,13 +6505,13 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6525,7 +6520,7 @@
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>75</v>
@@ -6567,7 +6562,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>84</v>
@@ -6590,10 +6585,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6616,13 +6611,13 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6673,7 +6668,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -6682,7 +6677,7 @@
         <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>96</v>
@@ -6696,10 +6691,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6722,16 +6717,16 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>214</v>
-      </c>
       <c r="M53" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6781,7 +6776,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -6796,18 +6791,18 @@
         <v>75</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>216</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6833,13 +6828,13 @@
         <v>78</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6889,7 +6884,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -6912,13 +6907,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>75</v>
@@ -6940,13 +6935,13 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6997,7 +6992,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7009,7 +7004,7 @@
         <v>75</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
@@ -7020,10 +7015,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7046,13 +7041,13 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7103,7 +7098,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7126,14 +7121,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7152,16 +7147,16 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7211,7 +7206,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7223,7 +7218,7 @@
         <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
@@ -7234,10 +7229,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7260,13 +7255,13 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7317,7 +7312,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7329,7 +7324,7 @@
         <v>75</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>75</v>
@@ -7340,10 +7335,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7366,13 +7361,13 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7381,7 +7376,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>75</v>
@@ -7423,7 +7418,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>84</v>
@@ -7446,10 +7441,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7472,13 +7467,13 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7529,7 +7524,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -7538,7 +7533,7 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>96</v>
@@ -7552,10 +7547,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7578,16 +7573,16 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7637,7 +7632,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -7646,7 +7641,7 @@
         <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>75</v>
@@ -7660,10 +7655,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7689,13 +7684,13 @@
         <v>78</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -7745,7 +7740,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -7768,13 +7763,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C63" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>75</v>
@@ -7796,13 +7791,13 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7853,7 +7848,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -7865,7 +7860,7 @@
         <v>75</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>75</v>
@@ -7876,10 +7871,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7902,13 +7897,13 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7959,7 +7954,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -7982,14 +7977,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8008,16 +8003,16 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8067,7 +8062,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8079,7 +8074,7 @@
         <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>75</v>
@@ -8090,10 +8085,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8116,13 +8111,13 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8173,7 +8168,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -8185,7 +8180,7 @@
         <v>75</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>75</v>
@@ -8196,10 +8191,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8222,13 +8217,13 @@
         <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8237,7 +8232,7 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>75</v>
@@ -8279,7 +8274,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>84</v>
@@ -8302,10 +8297,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8328,13 +8323,13 @@
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8385,7 +8380,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -8394,7 +8389,7 @@
         <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>96</v>
@@ -8408,10 +8403,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8434,16 +8429,16 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8493,7 +8488,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -8502,7 +8497,7 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>75</v>
@@ -8516,10 +8511,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8545,13 +8540,13 @@
         <v>78</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -8601,7 +8596,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>

--- a/StructureDefinition-access-align-in.xlsx
+++ b/StructureDefinition-access-align-in.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -644,7 +644,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.6</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.8</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -677,7 +677,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.6}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.8}
 </t>
   </si>
   <si>

--- a/StructureDefinition-access-align-in.xlsx
+++ b/StructureDefinition-access-align-in.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-align-in.xlsx
+++ b/StructureDefinition-access-align-in.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2386" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2657" uniqueCount="284">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -313,13 +313,187 @@
 </t>
   </si>
   <si>
-    <t>Parameters.implicitRules</t>
+    <t>Parameters.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Parameters.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Parameters.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Parameters.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Parameters.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Parameters.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Parameters.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Parameters.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Parameters.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -387,44 +561,7 @@
     <t>Parameters.parameter.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Parameters.parameter.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Parameters.parameter.modifierExtension</t>
@@ -644,7 +781,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.8</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.11</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -677,7 +814,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.8}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.11}
 </t>
   </si>
   <si>
@@ -1077,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL70"/>
+  <dimension ref="A1:AL78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.3828125" customWidth="true" bestFit="true"/>
@@ -1104,11 +1241,11 @@
     <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.64453125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.64453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="28.8359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -1464,7 +1601,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>84</v>
@@ -1579,10 +1716,10 @@
         <v>75</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>98</v>
@@ -1593,9 +1730,7 @@
       <c r="M5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>75</v>
@@ -1644,7 +1779,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -1656,32 +1791,32 @@
         <v>75</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>75</v>
@@ -1728,55 +1863,57 @@
         <v>75</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Y6" s="2"/>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1784,13 +1921,13 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>75</v>
@@ -1799,7 +1936,7 @@
         <v>85</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>114</v>
@@ -1807,7 +1944,9 @@
       <c r="M7" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="N7" s="2"/>
+      <c r="N7" t="s" s="2">
+        <v>116</v>
+      </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>75</v>
@@ -1844,29 +1983,31 @@
         <v>75</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC7" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="AF7" t="s" s="2">
-        <v>111</v>
-      </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
@@ -1877,10 +2018,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1900,18 +2041,20 @@
         <v>75</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>75</v>
@@ -1972,13 +2115,13 @@
         <v>75</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" hidden="true">
@@ -1990,14 +2133,14 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>75</v>
@@ -2006,19 +2149,19 @@
         <v>75</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2068,41 +2211,41 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>77</v>
@@ -2111,26 +2254,24 @@
         <v>75</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="N10" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>136</v>
-      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>75</v>
       </c>
@@ -2178,7 +2319,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2190,21 +2331,21 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2212,10 +2353,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>75</v>
@@ -2227,15 +2368,17 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M11" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>75</v>
@@ -2260,13 +2403,13 @@
         <v>75</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>75</v>
+        <v>141</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>75</v>
@@ -2284,13 +2427,13 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>75</v>
@@ -2307,10 +2450,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2321,7 +2464,7 @@
         <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>75</v>
@@ -2333,15 +2476,17 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>75</v>
@@ -2366,13 +2511,13 @@
         <v>75</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>75</v>
@@ -2390,16 +2535,16 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
@@ -2413,10 +2558,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2433,22 +2578,22 @@
         <v>75</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2498,7 +2643,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2507,10 +2652,10 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>75</v>
@@ -2521,10 +2666,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2535,7 +2680,7 @@
         <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>75</v>
@@ -2544,19 +2689,19 @@
         <v>75</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2582,13 +2727,11 @@
         <v>75</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>75</v>
@@ -2606,13 +2749,13 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>75</v>
@@ -2627,25 +2770,23 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>85</v>
@@ -2657,13 +2798,13 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2702,19 +2843,17 @@
         <v>75</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2726,7 +2865,7 @@
         <v>75</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
@@ -2737,10 +2876,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2763,13 +2902,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2820,7 +2959,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2843,14 +2982,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2869,16 +3008,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2928,7 +3067,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -2940,7 +3079,7 @@
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
@@ -2951,21 +3090,21 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>75</v>
+        <v>177</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>75</v>
@@ -2977,16 +3116,20 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
       </c>
@@ -3034,7 +3177,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3046,21 +3189,21 @@
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3074,7 +3217,7 @@
         <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>75</v>
@@ -3083,13 +3226,13 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3098,7 +3241,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>75</v>
@@ -3140,7 +3283,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -3161,12 +3304,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3174,13 +3317,13 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>75</v>
@@ -3189,13 +3332,13 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3246,7 +3389,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3255,10 +3398,10 @@
         <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>75</v>
@@ -3269,10 +3412,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3283,7 +3426,7 @@
         <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>75</v>
@@ -3295,16 +3438,16 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3354,7 +3497,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3363,7 +3506,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>75</v>
@@ -3377,10 +3520,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3403,16 +3546,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3462,7 +3605,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3485,13 +3628,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>75</v>
@@ -3513,13 +3656,13 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3570,7 +3713,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3582,7 +3725,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3593,10 +3736,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3619,13 +3762,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3676,7 +3819,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3699,14 +3842,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3725,16 +3868,16 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3784,7 +3927,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -3796,7 +3939,7 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
@@ -3807,10 +3950,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3833,13 +3976,13 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3890,7 +4033,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -3902,7 +4045,7 @@
         <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>75</v>
@@ -3913,10 +4056,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3939,13 +4082,13 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3954,7 +4097,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>75</v>
@@ -3996,7 +4139,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>84</v>
@@ -4019,10 +4162,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4045,13 +4188,13 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4102,7 +4245,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4111,10 +4254,10 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>96</v>
+        <v>210</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>75</v>
@@ -4125,10 +4268,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4151,16 +4294,16 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4210,7 +4353,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4219,7 +4362,7 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>75</v>
@@ -4233,10 +4376,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4262,13 +4405,13 @@
         <v>78</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4318,7 +4461,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4341,13 +4484,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>75</v>
@@ -4369,13 +4512,13 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4426,7 +4569,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4438,7 +4581,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
@@ -4449,10 +4592,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4475,13 +4618,13 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4532,7 +4675,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4555,14 +4698,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4581,16 +4724,16 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4640,7 +4783,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4652,7 +4795,7 @@
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
@@ -4663,10 +4806,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4689,13 +4832,13 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4746,7 +4889,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -4758,7 +4901,7 @@
         <v>75</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>75</v>
@@ -4769,10 +4912,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4795,13 +4938,13 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4810,7 +4953,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>75</v>
@@ -4852,7 +4995,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>84</v>
@@ -4873,12 +5016,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4886,13 +5029,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>75</v>
@@ -4901,13 +5044,13 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>143</v>
+        <v>209</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4958,7 +5101,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -4967,7 +5110,7 @@
         <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>96</v>
@@ -4979,44 +5122,44 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>186</v>
+        <v>75</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J37" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="K37" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5066,7 +5209,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5075,7 +5218,7 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>75</v>
@@ -5084,15 +5227,15 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>190</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5118,13 +5261,13 @@
         <v>78</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5174,7 +5317,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5197,13 +5340,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>75</v>
@@ -5225,13 +5368,13 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5282,7 +5425,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5294,7 +5437,7 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5305,10 +5448,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5331,13 +5474,13 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5388,7 +5531,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5411,14 +5554,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5437,16 +5580,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5496,7 +5639,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5508,7 +5651,7 @@
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>75</v>
@@ -5519,10 +5662,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5545,13 +5688,13 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5602,7 +5745,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5614,7 +5757,7 @@
         <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>75</v>
@@ -5625,10 +5768,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5651,13 +5794,13 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5666,7 +5809,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>75</v>
@@ -5708,7 +5851,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>84</v>
@@ -5729,12 +5872,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5742,13 +5885,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>75</v>
@@ -5757,13 +5900,13 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5790,11 +5933,13 @@
         <v>75</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>201</v>
+        <v>75</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -5812,7 +5957,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -5821,7 +5966,7 @@
         <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>96</v>
@@ -5833,44 +5978,44 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>149</v>
+        <v>232</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>150</v>
+        <v>233</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>151</v>
+        <v>233</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5920,7 +6065,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -5929,7 +6074,7 @@
         <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>75</v>
@@ -5938,15 +6083,15 @@
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>75</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5972,13 +6117,13 @@
         <v>78</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6028,7 +6173,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6051,13 +6196,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>75</v>
@@ -6067,7 +6212,7 @@
         <v>84</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>85</v>
@@ -6079,13 +6224,13 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6136,7 +6281,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6148,7 +6293,7 @@
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
@@ -6159,10 +6304,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6185,13 +6330,13 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6242,7 +6387,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6265,14 +6410,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6291,16 +6436,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6350,7 +6495,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6362,7 +6507,7 @@
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
@@ -6373,10 +6518,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6399,13 +6544,13 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6456,7 +6601,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6468,7 +6613,7 @@
         <v>75</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>75</v>
@@ -6479,10 +6624,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6505,13 +6650,13 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6520,7 +6665,7 @@
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>75</v>
@@ -6562,7 +6707,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>84</v>
@@ -6583,12 +6728,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6596,13 +6741,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>75</v>
@@ -6611,13 +6756,13 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>143</v>
+        <v>243</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6644,13 +6789,11 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>75</v>
+        <v>245</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -6668,7 +6811,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -6677,7 +6820,7 @@
         <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>96</v>
@@ -6689,12 +6832,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6702,31 +6845,31 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="K53" t="s" s="2">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6776,7 +6919,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -6785,24 +6928,24 @@
         <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>214</v>
+        <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>215</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6828,13 +6971,13 @@
         <v>78</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6884,7 +7027,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -6907,13 +7050,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>75</v>
@@ -6923,7 +7066,7 @@
         <v>84</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>85</v>
@@ -6935,13 +7078,13 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6992,7 +7135,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7004,7 +7147,7 @@
         <v>75</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
@@ -7015,10 +7158,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7041,13 +7184,13 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7098,7 +7241,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7121,14 +7264,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7147,16 +7290,16 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7206,7 +7349,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7218,7 +7361,7 @@
         <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
@@ -7229,10 +7372,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7255,13 +7398,13 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7312,7 +7455,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7324,7 +7467,7 @@
         <v>75</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>75</v>
@@ -7335,10 +7478,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7361,13 +7504,13 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7376,7 +7519,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>75</v>
@@ -7418,7 +7561,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>84</v>
@@ -7439,12 +7582,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7452,13 +7595,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>75</v>
@@ -7467,13 +7610,13 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>226</v>
+        <v>187</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7524,7 +7667,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -7533,7 +7676,7 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>96</v>
@@ -7545,12 +7688,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7558,31 +7701,31 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>148</v>
+        <v>256</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>149</v>
+        <v>257</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>150</v>
+        <v>233</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>151</v>
+        <v>233</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7632,7 +7775,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -7641,24 +7784,24 @@
         <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>75</v>
+        <v>258</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>75</v>
+        <v>259</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7684,13 +7827,13 @@
         <v>78</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -7740,7 +7883,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -7763,20 +7906,20 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>84</v>
@@ -7791,13 +7934,13 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7848,7 +7991,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -7860,7 +8003,7 @@
         <v>75</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>75</v>
@@ -7871,10 +8014,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7897,13 +8040,13 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7954,7 +8097,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -7977,14 +8120,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8003,16 +8146,16 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8062,7 +8205,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8074,7 +8217,7 @@
         <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>75</v>
@@ -8085,10 +8228,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8111,13 +8254,13 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8168,7 +8311,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -8180,7 +8323,7 @@
         <v>75</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>75</v>
@@ -8191,10 +8334,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8217,13 +8360,13 @@
         <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8232,7 +8375,7 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>75</v>
@@ -8274,7 +8417,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>84</v>
@@ -8297,10 +8440,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8323,13 +8466,13 @@
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8380,7 +8523,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -8389,7 +8532,7 @@
         <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>96</v>
@@ -8403,10 +8546,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8429,16 +8572,16 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8488,7 +8631,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -8497,7 +8640,7 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>75</v>
@@ -8511,10 +8654,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8540,13 +8683,13 @@
         <v>78</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -8596,7 +8739,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -8617,8 +8760,864 @@
         <v>75</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="D71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL70">
+  <autoFilter ref="A1:AL78">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8628,7 +9627,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI77">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-access-align-in.xlsx
+++ b/StructureDefinition-access-align-in.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-align-in.xlsx
+++ b/StructureDefinition-access-align-in.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -781,7 +781,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.11</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.12</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -814,7 +814,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.11}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition|0.9.12}
 </t>
   </si>
   <si>
